--- a/downloads/xlsx/个人机会与申请进度.xlsx
+++ b/downloads/xlsx/个人机会与申请进度.xlsx
@@ -545,7 +545,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>docs/timelines（本科四年时间线）</t>
+          <t>docs/timelines/本科四年.md</t>
         </is>
       </c>
     </row>
